--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Neighbors sandoq | Family circle</t>
+          <t>Neighbors sandoq | Family circle | Office lunch fund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Neighbors sandoq</t>
+          <t>Neighbors sandoq | Office lunch fund</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -886,7 +886,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pilot circle | Community sandoq | Family circle</t>
+          <t>Pilot circle | Community sandoq | Family circle | Office lunch fund</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -907,10 +907,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GDVCPWNF6GSOQJ6FOXEICVSRUMZY73SJBUDAIVZAYJEU6T46PZA6KIRP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Office lunch fund</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
@@ -919,25 +923,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>exploring</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>what did you do ?</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-07-25T20:50:38.000Z</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://stellar.expert/explorer/testnet/account/GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GDVCPWNF6GSOQJ6FOXEICVSRUMZY73SJBUDAIVZAYJEU6T46PZA6KIRP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>organizer</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>The UI and UX were both great, and everything felt smooth and intuitive to use</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-07-19T17:39:27.000Z</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://stellar.expert/explorer/testnet/account/GDVCPWNF6GSOQJ6FOXEICVSRUMZY73SJBUDAIVZAYJEU6T46PZA6KIRP</t>
         </is>

--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -518,32 +518,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google Form</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSd-xWgr5Y-mCbFkxkCJxT8Jq3lwpHHj1JbRVZPpLPmY-POSng/viewform</t>
-        </is>
+          <t>Google Form responses</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>responses paste into the 'Form responses' sheet</t>
+          <t>docs/form-responses.csv, from the form's export</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Form responses whose wallet is also on-chain</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>the form's wallet column matched against testnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google Form</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSd-xWgr5Y-mCbFkxkCJxT8Jq3lwpHHj1JbRVZPpLPmY-POSng/viewform</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>import with: build-workbook.py --form &lt;export&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Regenerate</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>node scripts/export-users.mjs &amp;&amp; python scripts/build-workbook.py</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>reads live testnet state</t>
         </is>

--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1082,6 +1082,414 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7/25/2026 0:49:53</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>base.kiki.111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kiki</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gwerfijq4wihj348hj4roiwqth[4pht4[oqith4q3o[jit4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Started a circle</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>really amazing</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7/25/2026 0:53:59</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>shynrzee1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>shakhan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GB237RO6DJ2OS5CXAQI63QZ3IVM4FETD7RYOETALEWXVIYD6SXZ7H775</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Joined a circle</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I think with a little more polish on the UI, everything would be spot on</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7/25/2026 0:57:33</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jp.sullione@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sulli1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GCGB7RRMZGLDXU2OYVNYWA33ZDNS3FV6YW4N4LGNCLUHKM6LNC2MLVUJ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Just explored</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>the better UI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7/25/2026 0:58:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mo.g.banzaan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>banzaan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GCKEHLIRP6ETZLI7JH4TSFCJH7J3U6MOILLNEM3IWHJLSGN6OUHMO3VR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Joined a circle</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>mainnet make it better</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7/26/2026 10:14:32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sadiyamulani03@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sadiya Mulani</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GBTCGV43NLHEEBMCA5DWFZT6GOJYYCPHXNOEALTBQ7TREIQKQQAVLYT4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Just explored</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>All good</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7/26/2026 20:45:18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>degirmenseyit@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>seyit ali değirmen</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GDOCMYNNTH62NW37IZCN6BKQTM5Z73RW7OOFXRADLYXUABDN3UXWDTNC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Started a circle</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7/27/2026 0:55:29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>vahshiking@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zeus</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GCUGKNYWZDXQCBA6GVDD4IEHEF6PUCFWKVOGBTONSTIMSPHFILWUWSKJ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Joined a circle</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Its good but can be better and simple to use</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7/27/2026 1:01:32</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>vahshiking0@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hakak</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GCJ66XRESW4ZODGGF7AQQGTGLCBRXCLJRZSSSHNLRX7Q4TC7DUH6P6M6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Joined a circle</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sandali avalo befrosh  jash kandom bekhar :/</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7/27/2026 1:11:51</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hossainialisina011@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Alisina</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GA5ONRZ2INQIXSGGDTXPWSWR5YII254MV5DJYYLOZQSKPZFTNP2VYMKO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Add stablecoin too</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7/27/2026 1:45:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>alirezayat9@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ali Rezayat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GB2K4VQVHGLLTNM6J7MFPFANINEOQQJCCZUO6B5NHQX7GHCTZU6W5MHS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Started a circle</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Really enjoyed it but the UI could've been better</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="On-chain activity" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Form responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On-chain activity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form responses" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -695,55 +695,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GBQAORFEFKDPXX7IQ5INBDMY7YNRVNSZGKJHTGXJK3PN2OQEYMPYJEKV</t>
+          <t>GB2K4VQVHGLLTNM6J7MFPFANINEOQQJCCZUO6B5NHQX7GHCTZU6W5MHS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pilot circle</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Abbaas circle</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Abbaas circle</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>exploring</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>wow, i was an amazing time</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-07-20T18:04:09.000Z</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GBQAORFEFKDPXX7IQ5INBDMY7YNRVNSZGKJHTGXJK3PN2OQEYMPYJEKV</t>
+          <t>https://stellar.expert/explorer/testnet/account/GB2K4VQVHGLLTNM6J7MFPFANINEOQQJCCZUO6B5NHQX7GHCTZU6W5MHS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GBTTVCNCTB6GOZJYBQ5A7PIVSFA6BAQ3LVQ2AKQWKFAWSVP2PXSWP2FO</t>
+          <t>GBQAORFEFKDPXX7IQ5INBDMY7YNRVNSZGKJHTGXJK3PN2OQEYMPYJEKV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neighbors sandoq</t>
+          <t>Pilot circle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -754,37 +742,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>exploring</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Clear seat order. The next-payout highlight helped.</t>
+          <t>wow, i was an amazing time</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-19T16:17:39.000Z</t>
+          <t>2026-07-20T18:04:09.000Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GBTTVCNCTB6GOZJYBQ5A7PIVSFA6BAQ3LVQ2AKQWKFAWSVP2PXSWP2FO</t>
+          <t>https://stellar.expert/explorer/testnet/account/GBQAORFEFKDPXX7IQ5INBDMY7YNRVNSZGKJHTGXJK3PN2OQEYMPYJEKV</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCT2EGRCG7W5T3HGG2DFR2PBR65BZHIUBLO6DP3SVGHXTBIXNH3SX7YT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>GBTTVCNCTB6GOZJYBQ5A7PIVSFA6BAQ3LVQ2AKQWKFAWSVP2PXSWP2FO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Neighbors sandoq</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
@@ -793,88 +785,68 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>organizer</t>
+          <t>member</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Everything is ok</t>
+          <t>Clear seat order. The next-payout highlight helped.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-19T17:47:03.000Z</t>
+          <t>2026-07-19T16:17:39.000Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GCT2EGRCG7W5T3HGG2DFR2PBR65BZHIUBLO6DP3SVGHXTBIXNH3SX7YT</t>
+          <t>https://stellar.expert/explorer/testnet/account/GBTTVCNCTB6GOZJYBQ5A7PIVSFA6BAQ3LVQ2AKQWKFAWSVP2PXSWP2FO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GD3JZYUP3DFKCWSGLRR2SBKJYRVTVBEX3IIELUPE2TA6ZIC2T7U7UHNH</t>
+          <t>GBX57U74O7VTIBHK7ZFN5TJ4TLRRTOOXENJAZNA2B25MDUF54DVWMY5Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Neighbors sandoq | Family circle | Office lunch fund</t>
+          <t>Pilot circle | Abbaas circle | Banban</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Neighbors sandoq</t>
+          <t>Banban</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>organizer</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Loved how my collateral came straight back. Deploying a circle from the UI just worked.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-19T16:17:19.000Z</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GD3JZYUP3DFKCWSGLRR2SBKJYRVTVBEX3IIELUPE2TA6ZIC2T7U7UHNH</t>
+          <t>https://stellar.expert/explorer/testnet/account/GBX57U74O7VTIBHK7ZFN5TJ4TLRRTOOXENJAZNA2B25MDUF54DVWMY5Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GD4DCCECPN4M6F6YD6NNQDUD6M4NOOCXYYP4CGBKJE53FD456TCHT53S</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Neighbors sandoq | Office lunch fund</t>
-        </is>
-      </c>
+          <t>GCT2EGRCG7W5T3HGG2DFR2PBR65BZHIUBLO6DP3SVGHXTBIXNH3SX7YT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
@@ -883,66 +855,86 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>organizer</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Joining was smooth. Wanted a reminder before the round closes.</t>
+          <t>Everything is ok</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-19T16:17:29.000Z</t>
+          <t>2026-07-19T17:47:03.000Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GD4DCCECPN4M6F6YD6NNQDUD6M4NOOCXYYP4CGBKJE53FD456TCHT53S</t>
+          <t>https://stellar.expert/explorer/testnet/account/GCT2EGRCG7W5T3HGG2DFR2PBR65BZHIUBLO6DP3SVGHXTBIXNH3SX7YT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GDGMCDU5HPC2Z7B6XO67IO5AZZR6NRITVS3E47WJ7LAQJBNAX2I2NJTC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>GD3JZYUP3DFKCWSGLRR2SBKJYRVTVBEX3IIELUPE2TA6ZIC2T7U7UHNH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Neighbors sandoq | Family circle | Office lunch fund</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pilot circle | Community sandoq | Family circle | Office lunch fund</t>
+          <t>Neighbors sandoq</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>organizer</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Loved how my collateral came straight back. Deploying a circle from the UI just worked.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-07-19T16:17:19.000Z</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GDGMCDU5HPC2Z7B6XO67IO5AZZR6NRITVS3E47WJ7LAQJBNAX2I2NJTC</t>
+          <t>https://stellar.expert/explorer/testnet/account/GD3JZYUP3DFKCWSGLRR2SBKJYRVTVBEX3IIELUPE2TA6ZIC2T7U7UHNH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+          <t>GD4DCCECPN4M6F6YD6NNQDUD6M4NOOCXYYP4CGBKJE53FD456TCHT53S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Office lunch fund</t>
+          <t>Neighbors sandoq | Office lunch fund</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -958,59 +950,160 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>exploring</t>
+          <t>member</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>what did you do ?</t>
+          <t>Joining was smooth. Wanted a reminder before the round closes.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-25T20:50:38.000Z</t>
+          <t>2026-07-19T16:17:29.000Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://stellar.expert/explorer/testnet/account/GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+          <t>https://stellar.expert/explorer/testnet/account/GD4DCCECPN4M6F6YD6NNQDUD6M4NOOCXYYP4CGBKJE53FD456TCHT53S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>GDGMCDU5HPC2Z7B6XO67IO5AZZR6NRITVS3E47WJ7LAQJBNAX2I2NJTC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pilot circle | Community sandoq | Family circle | Office lunch fund | Trustless circle</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://stellar.expert/explorer/testnet/account/GDGMCDU5HPC2Z7B6XO67IO5AZZR6NRITVS3E47WJ7LAQJBNAX2I2NJTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Office lunch fund</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>exploring</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>it have realy good idea behind it</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-07-25T21:06:40.000Z</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://stellar.expert/explorer/testnet/account/GDJYZWEEPQ7QHAYRUL3LP64U5HWCWONT5DMMKRQBOLU4K5LC5VN2F25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GDOCMYNNTH62NW37IZCN6BKQTM5Z73RW7OOFXRADLYXUABDN3UXWDTNC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ssay</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ssay</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://stellar.expert/explorer/testnet/account/GDOCMYNNTH62NW37IZCN6BKQTM5Z73RW7OOFXRADLYXUABDN3UXWDTNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>GDVCPWNF6GSOQJ6FOXEICVSRUMZY73SJBUDAIVZAYJEU6T46PZA6KIRP</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>organizer</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>The UI and UX were both great, and everything felt smooth and intuitive to use</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-07-19T17:39:27.000Z</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://stellar.expert/explorer/testnet/account/GDVCPWNF6GSOQJ6FOXEICVSRUMZY73SJBUDAIVZAYJEU6T46PZA6KIRP</t>
         </is>
